--- a/Data belum ketemu.xlsx
+++ b/Data belum ketemu.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\SIGMA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5E54BA-6ADD-4061-9D6F-A98E34CF452C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8BB8F7-3712-4ABB-9A4E-0E12E87A84AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D4C245F-0977-412C-8AA5-58D47CB26E8E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="212">
   <si>
     <t>Nama</t>
   </si>
@@ -1524,7 +1524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1663,8 +1663,11 @@
       <c r="D42" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E42" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1678,7 +1681,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1692,7 +1695,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -1706,7 +1709,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -1734,7 +1737,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>47</v>
       </c>
